--- a/data/trans_camb/IP1006-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Edad-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,0</t>
+          <t>-2,21; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,75</t>
+          <t>-1,13; 0,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,21</t>
+          <t>-0,28; 2,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,0</t>
+          <t>-0,37; 1,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,65</t>
+          <t>-0,49; 0,69</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,0</t>
+          <t>-2,67; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,44</t>
+          <t>-0,85; 0,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,32</t>
+          <t>-1,02; 0,32</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,86</t>
+          <t>-1,4; 0,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,29</t>
+          <t>-1,04; 2,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,77</t>
+          <t>-0,31; 3,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,0</t>
+          <t>-1,7; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,72</t>
+          <t>-0,62; 1,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,87</t>
+          <t>-0,84; 0,93</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,28</t>
+          <t>-0,64; 0,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,53</t>
+          <t>-0,5; 0,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,22</t>
+          <t>-0,06; 1,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,42</t>
+          <t>-0,5; 0,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,59</t>
+          <t>-0,21; 0,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,37</t>
+          <t>-0,34; 0,32</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,57; 484,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,75; 1173,73</t>
+          <t>-43,27; 1169,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,77; 337,14</t>
+          <t>-54,41; 346,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 237,81</t>
+          <t>-71,35; 206,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Edad-trans_camb.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,0</t>
+          <t>-1,85; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,53</t>
+          <t>-1,14; 0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,11</t>
+          <t>-0,27; 2,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,99</t>
+          <t>-0,57; 0,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,05</t>
+          <t>-0,44; 1,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,69</t>
+          <t>-0,59; 0,64</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,0</t>
+          <t>-2,55; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,44</t>
+          <t>-0,86; 0,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,32</t>
+          <t>-1,31; 0,32</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,85</t>
+          <t>-1,67; 0,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,04</t>
+          <t>-1,05; 2,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,33</t>
+          <t>-0,29; 3,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,63</t>
+          <t>-0,49; 1,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,93</t>
+          <t>-0,84; 0,84</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,28</t>
+          <t>-0,64; 0,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,5</t>
+          <t>-0,5; 0,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,21</t>
+          <t>-0,03; 1,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,37</t>
+          <t>-0,5; 0,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,58</t>
+          <t>-0,2; 0,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,32</t>
+          <t>-0,38; 0,32</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,57; 484,36</t>
+          <t>-87,51; 541,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 1169,96</t>
+          <t>-37,87; 1571,15</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,41; 346,45</t>
+          <t>-46,99; 374,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-71,35; 206,39</t>
+          <t>-72,96; 223,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,6</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,78</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,21</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,0</t>
+          <t>-0,27; 2,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,56</t>
+          <t>-0,57; 0,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,12</t>
+          <t>-1,43; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,98</t>
+          <t>-1,13; 0,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,03</t>
+          <t>-0,37; 1,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,64</t>
+          <t>-0,58; 0,65</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>289,64%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-44,7%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>289,64%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,32</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>-2,54; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>-2,56; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,0</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,0</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,44</t>
+          <t>-0,82; 0,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,32</t>
+          <t>-1,07; 0,32</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,06</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,19</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,82</t>
+          <t>-0,28; 3,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,08</t>
+          <t>-1,68; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,35</t>
+          <t>-1,39; 0,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,0</t>
+          <t>-1,04; 2,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,64</t>
+          <t>-0,48; 1,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,84</t>
+          <t>-0,84; 0,87</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>315,85%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-44,32%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>28,03%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>315,85%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,01</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,21</t>
+          <t>-0,14; 1,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,56</t>
+          <t>-0,51; 0,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,25</t>
+          <t>-0,66; 0,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,41</t>
+          <t>-0,5; 0,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,6</t>
+          <t>-0,18; 0,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,32</t>
+          <t>-0,33; 0,37</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>170,87%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-7,64%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-48,35%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>170,87%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-7,64%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-54,75; 1173,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-87,51; 541,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 1571,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 374,3</t>
+          <t>-41,77; 337,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-72,96; 223,54</t>
+          <t>-71,43; 237,81</t>
         </is>
       </c>
     </row>
